--- a/progresso.xlsx
+++ b/progresso.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_git\FOLDER_TCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{111E42EF-EC19-4F74-BD8F-110E5E66DB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D84AAFF-8C09-4B5A-8FEF-65B883063AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -458,7 +458,7 @@
         <v>3</v>
       </c>
       <c r="D3" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
@@ -491,7 +491,7 @@
         <v>4</v>
       </c>
       <c r="D6" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
@@ -502,7 +502,7 @@
         <v>2</v>
       </c>
       <c r="D7" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
@@ -526,11 +526,11 @@
       </c>
       <c r="D9" s="2">
         <f>SUM(D2:D8)</f>
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E9" s="4">
         <f>(D9/C9)</f>
-        <v>0.57894736842105265</v>
+        <v>0.89473684210526316</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">

--- a/progresso.xlsx
+++ b/progresso.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\_git\FOLDER_TCC\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D84AAFF-8C09-4B5A-8FEF-65B883063AEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF913A00-B810-4023-AE04-0B01DD6B4A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
@@ -513,7 +513,7 @@
         <v>2</v>
       </c>
       <c r="D8" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
@@ -526,11 +526,11 @@
       </c>
       <c r="D9" s="2">
         <f>SUM(D2:D8)</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E9" s="4">
         <f>(D9/C9)</f>
-        <v>0.89473684210526316</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
